--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484066_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484066_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.6148</v>
+        <v>12.691</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1173</v>
+        <v>11.4461</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4974</v>
+        <v>1.2449</v>
       </c>
       <c r="G2" t="n">
         <v>8.3994</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0153</v>
+        <v>0.0609</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6914</v>
+        <v>-0.3626</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6761</v>
+        <v>0.4236</v>
       </c>
       <c r="V2" t="n">
         <v>4.8259</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9864</v>
+        <v>4.3996</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4259</v>
+        <v>4.4283</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5604</v>
+        <v>-0.0288</v>
       </c>
       <c r="G3" t="n">
         <v>2.3269</v>
@@ -688,13 +688,13 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4016</v>
+        <v>0.8148</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5986</v>
+        <v>0.6009</v>
       </c>
       <c r="U3" t="n">
-        <v>0.803</v>
+        <v>0.2138</v>
       </c>
       <c r="V3" t="n">
         <v>0.266</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0514</v>
+        <v>0.1348</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4334</v>
+        <v>0.5354</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4847</v>
+        <v>-0.4006</v>
       </c>
       <c r="G4" t="n">
         <v>1.0253</v>
@@ -766,13 +766,13 @@
         <v>0.5952</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4653</v>
+        <v>-0.2792</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2494</v>
+        <v>-0.1474</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.216</v>
+        <v>-0.1318</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2065</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6873</v>
+        <v>-0.7259</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9816</v>
+        <v>0.4941</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6689</v>
+        <v>-1.22</v>
       </c>
       <c r="G5" t="n">
         <v>3.7746</v>
@@ -844,13 +844,13 @@
         <v>2.3806</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2165</v>
+        <v>-0.2551</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6066</v>
+        <v>0.1192</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.3742</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6745</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.954</v>
+        <v>-0.778</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6455</v>
+        <v>-0.4414</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3086</v>
+        <v>-0.3366</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8555</v>
@@ -922,13 +922,13 @@
         <v>0.1984</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5629</v>
+        <v>-0.3869</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3117</v>
+        <v>-0.1077</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2511</v>
+        <v>-0.2792</v>
       </c>
       <c r="V6" t="n">
         <v>0.266</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6396</v>
+        <v>-1.2917</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4023</v>
+        <v>0.41</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7627</v>
+        <v>-1.7017</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4476</v>
+        <v>-1.2794</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2623</v>
+        <v>-1.4219</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1853</v>
+        <v>0.1425</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0803</v>
+        <v>0.365</v>
       </c>
       <c r="K7" t="n">
+        <v>0.2419</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1.6443</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1.6638</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.3887</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0.0803</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-0.5279</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-0.2623</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.2656</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-1.3887</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4778</v>
+        <v>-0.4605</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4988</v>
+        <v>-0.221</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0209</v>
+        <v>-0.2395</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6745</v>
+        <v>-0.9405</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6745</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4392</v>
+        <v>-1.5656</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4289</v>
+        <v>-2.3002</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0103</v>
+        <v>0.7347</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2794</v>
+        <v>-0.4476</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4219</v>
+        <v>-0.2623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1425</v>
+        <v>-0.1853</v>
       </c>
       <c r="J8" t="n">
-        <v>0.365</v>
+        <v>0.0803</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2419</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.123</v>
+        <v>0.0803</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6443</v>
+        <v>-0.5279</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6638</v>
+        <v>-0.2623</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0195</v>
+        <v>-0.2656</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3887</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q8" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.5952</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.4038</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.3967</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.6745</v>
+      </c>
+      <c r="W8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.3887</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-1.608</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-1.0599</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.5481</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.9405</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.266</v>
-      </c>
       <c r="X8" t="n">
-        <v>-1.2065</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5619</v>
+        <v>-1.6311</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3654</v>
+        <v>-0.3225</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1964</v>
+        <v>-1.3087</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8445</v>
@@ -1156,13 +1156,13 @@
         <v>2.1822</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4352</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.621</v>
+        <v>-0.578</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1858</v>
+        <v>0.0735</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4724</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. NEBRA SANCHEZ</t>
+          <t>B. PAÑART POSTIGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0663</v>
+        <v>-3.8069</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7994</v>
+        <v>-2.8896</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2669</v>
+        <v>-0.9173</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5254</v>
+        <v>-2.5414</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5796</v>
+        <v>-0.7663</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9458</v>
+        <v>-1.775</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-2.5723</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3173</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6802</v>
+        <v>-1.9175</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5279</v>
+        <v>0.0309</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2623</v>
+        <v>-0.1116</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2656</v>
+        <v>0.1425</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0623</v>
+        <v>-0.4478</v>
       </c>
       <c r="T10" t="n">
-        <v>0.924</v>
+        <v>-0.3174</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1383</v>
+        <v>-0.1304</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8097</v>
       </c>
       <c r="W10" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.0757</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. PAÑART POSTIGO</t>
+          <t>J. NEBRA SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3375</v>
+        <v>-3.9387</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1957</v>
+        <v>-1.6157</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1417</v>
+        <v>-2.323</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5414</v>
+        <v>-1.5254</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7663</v>
+        <v>-0.5796</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.775</v>
+        <v>-0.9458</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5723</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.3173</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9175</v>
+        <v>-0.6802</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0309</v>
+        <v>-0.5279</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1116</v>
+        <v>-0.2623</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1425</v>
+        <v>-0.2656</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9919</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9782999999999999</v>
+        <v>0.1899</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.1077</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3549</v>
+        <v>0.0822</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8097</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8097</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.863999999999997</v>
+        <v>3.4875</v>
       </c>
       <c r="E12" t="n">
-        <v>9.120999999999999</v>
+        <v>9.7445</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.257</v>
+        <v>-6.257099999999999</v>
       </c>
       <c r="G12" t="n">
         <v>8.032400000000001</v>
@@ -1372,16 +1372,16 @@
         <v>13.9265</v>
       </c>
       <c r="M12" t="n">
-        <v>-8.0672</v>
+        <v>-8.067200000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-8.877199999999998</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8100999999999999</v>
+        <v>0.8101</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9919</v>
+        <v>-0.9918999999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.8868</v>
@@ -1390,13 +1390,13 @@
         <v>12.895</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.295399999999999</v>
+        <v>-1.6722</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9265</v>
+        <v>-1.303</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3691000000000001</v>
+        <v>-0.3690999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8809</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.4554</v>
+        <v>5.4684</v>
       </c>
       <c r="E13" t="n">
-        <v>6.4207</v>
+        <v>4.6862</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0347</v>
+        <v>0.7822</v>
       </c>
       <c r="G13" t="n">
         <v>3.1171</v>
@@ -1468,13 +1468,13 @@
         <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4139</v>
+        <v>1.4269</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6018</v>
+        <v>0.8673</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8121</v>
+        <v>0.5596</v>
       </c>
       <c r="V13" t="n">
         <v>-0.266</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5651</v>
+        <v>1.0854</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0144</v>
+        <v>2.4225</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4493</v>
+        <v>-1.3371</v>
       </c>
       <c r="G14" t="n">
         <v>-1.7927</v>
@@ -1546,13 +1546,13 @@
         <v>1.9838</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7811</v>
+        <v>-0.2607</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.5894</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2165</v>
+        <v>0.3287</v>
       </c>
       <c r="V14" t="n">
         <v>2.1469</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BELTRAN MATA</t>
+          <t>I. VILLAR CANTERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0931</v>
+        <v>0.8388</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3856</v>
+        <v>0.3403</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4787</v>
+        <v>0.4985</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.7501</v>
+        <v>0.2149</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1263</v>
+        <v>-0.2269</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.8764</v>
+        <v>0.4418</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.85</v>
+        <v>0.0512</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3035</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.1534</v>
+        <v>0.5648</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9002</v>
+        <v>0.1637</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1772</v>
+        <v>0.2867</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.723</v>
+        <v>-0.123</v>
       </c>
       <c r="P15" t="n">
         <v>0.7935</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2878</v>
+        <v>0.0964</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9238</v>
+        <v>0.2891</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.364</v>
+        <v>-0.1928</v>
       </c>
       <c r="V15" t="n">
-        <v>4.1513</v>
+        <v>-0.266</v>
       </c>
       <c r="W15" t="n">
-        <v>4.1513</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. VILLAR CANTERO</t>
+          <t>A. BELTRAN MATA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.212</v>
+        <v>0.7895</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3739</v>
+        <v>1.0999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1618</v>
+        <v>-0.3104</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2149</v>
+        <v>-3.7501</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2269</v>
+        <v>0.1263</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4418</v>
+        <v>-3.8764</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0512</v>
+        <v>-1.85</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5135999999999999</v>
+        <v>0.3035</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5648</v>
+        <v>-2.1534</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1637</v>
+        <v>-1.9002</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2867</v>
+        <v>-0.1772</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.123</v>
+        <v>-1.723</v>
       </c>
       <c r="P16" t="n">
         <v>0.7935</v>
       </c>
       <c r="Q16" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.7855</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.4053</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.2096</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.1957</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.1513</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.1513</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.7935</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-0.9545</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.4251</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.5294</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.266</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.266</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3231</v>
+        <v>-0.0196</v>
       </c>
       <c r="E17" t="n">
-        <v>0.625</v>
+        <v>1.2371</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-1.2567</v>
       </c>
       <c r="G17" t="n">
         <v>0.2463</v>
@@ -1780,13 +1780,13 @@
         <v>2.1822</v>
       </c>
       <c r="S17" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.3132</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6291</v>
+        <v>-0.0169</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="V17" t="n">
         <v>1.2065</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. MARTÍN LLAVERÍA</t>
+          <t>A. CRUZ JOBACHO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1894</v>
+        <v>-1.3349</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.3079</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0986</v>
+        <v>-1.6428</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6243</v>
+        <v>1.2699</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6779</v>
+        <v>-0.4234</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.3022</v>
+        <v>1.6933</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9609</v>
+        <v>0.988</v>
       </c>
       <c r="K18" t="n">
-        <v>1.996</v>
+        <v>-0.2971</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0351</v>
+        <v>1.2852</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5853</v>
+        <v>0.2818</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3181</v>
+        <v>-0.1263</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2672</v>
+        <v>0.4081</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2284</v>
+        <v>0.0227</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0679</v>
+        <v>-0.0056</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2964</v>
+        <v>0.0283</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-3.6194</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.9449</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>L. MARTÍN LLAVERÍA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5131</v>
+        <v>-1.3654</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3936</v>
+        <v>-0.2949</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9067</v>
+        <v>-1.0705</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6905</v>
+        <v>-0.6243</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4134</v>
+        <v>1.6779</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.104</v>
+        <v>-2.3022</v>
       </c>
       <c r="J19" t="n">
-        <v>0.298</v>
+        <v>1.9609</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.996</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.64</v>
+        <v>-0.0351</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9885</v>
+        <v>-2.5853</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5246</v>
+        <v>-0.3181</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4639</v>
+        <v>-2.2672</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9919</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1694</v>
+        <v>0.0524</v>
       </c>
       <c r="T19" t="n">
-        <v>0.873</v>
+        <v>-0.272</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2964</v>
+        <v>0.3244</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CRUZ JOBACHO</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5288</v>
+        <v>-2.0972</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0018</v>
+        <v>-0.2186</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5306</v>
+        <v>-1.8786</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2699</v>
+        <v>-1.6905</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4234</v>
+        <v>0.4134</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6933</v>
+        <v>-2.104</v>
       </c>
       <c r="J20" t="n">
-        <v>0.988</v>
+        <v>0.298</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2971</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2852</v>
+        <v>-0.64</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2818</v>
+        <v>-1.9885</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1263</v>
+        <v>-0.5246</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4081</v>
+        <v>-1.4639</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9919</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
         <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1712</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3117</v>
+        <v>0.2608</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1405</v>
+        <v>0.3244</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.6194</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6745</v>
+        <v>1.2065</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.9449</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.0249</v>
+        <v>-6.229</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1195</v>
+        <v>-3.3235</v>
       </c>
       <c r="F21" t="n">
         <v>-2.9055</v>
@@ -2092,10 +2092,10 @@
         <v>1.7855</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6688</v>
+        <v>0.4648</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2495</v>
+        <v>0.0455</v>
       </c>
       <c r="U21" t="n">
         <v>0.4193</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8639</v>
+        <v>-2.864</v>
       </c>
       <c r="E22" t="n">
-        <v>6.2569</v>
+        <v>6.256900000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-9.121</v>
+        <v>-9.120899999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-8.032299999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>6.704200000000002</v>
+        <v>6.7042</v>
       </c>
       <c r="I22" t="n">
         <v>-14.7368</v>
@@ -2149,7 +2149,7 @@
         <v>8.8773</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8103000000000001</v>
+        <v>-0.8103</v>
       </c>
       <c r="M22" t="n">
         <v>-16.0996</v>
@@ -2170,13 +2170,13 @@
         <v>13.8868</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2955</v>
+        <v>2.2956</v>
       </c>
       <c r="T22" t="n">
         <v>0.3691999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9264</v>
+        <v>1.9262</v>
       </c>
       <c r="V22" t="n">
         <v>1.880899999999999</v>
